--- a/currentbuild/ValueSet-no-basis-encounter-auditevent-servicetype.xlsx
+++ b/currentbuild/ValueSet-no-basis-encounter-auditevent-servicetype.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-17T09:59:20+00:00</t>
+    <t>2024-04-06T16:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -71,13 +71,13 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Norway (https://github.com/HL7Norway)</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Valueset for Encounter.serviceType used in context of auditevent. See [volven.no](https://volven.no/) for definition.</t>
+    <t>Valueset for Encounter.serviceType used in context of auditevent. See [volven.no](https://volven.no/) or [FinnKode](https://beta.finnkode.ehelse.no/adm/collections) for definition.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/currentbuild/ValueSet-no-basis-encounter-auditevent-servicetype.xlsx
+++ b/currentbuild/ValueSet-no-basis-encounter-auditevent-servicetype.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -44,7 +44,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AuditEvent Encounter.servicetype valueset</t>
+    <t>AuditEvent encounter.servicetype valueset</t>
   </si>
   <si>
     <t>Status</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-06T16:49:55+00:00</t>
+    <t>2024-04-28T16:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-no-basis-encounter-auditevent-servicetype.xlsx
+++ b/currentbuild/ValueSet-no-basis-encounter-auditevent-servicetype.xlsx
@@ -26,13 +26,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:no-basis-auditevent/ValueSet/no-basis-encounter-auditevent-servicetype</t>
+    <t>http://hl7.no/fhir/ValueSet/no-basis-encounter-auditevent-servicetype</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -50,7 +50,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-28T16:36:28+00:00</t>
+    <t>2024-06-04T05:44:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-no-basis-encounter-auditevent-servicetype.xlsx
+++ b/currentbuild/ValueSet-no-basis-encounter-auditevent-servicetype.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T05:44:14+00:00</t>
+    <t>2024-06-04T06:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
